--- a/testcasecuadat.xlsx
+++ b/testcasecuadat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huudat/KTPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79D55417-0A2F-3445-A068-4E67E6626C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8DAA0C-8B1A-6D47-AE5B-6495C3928675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="16920" xr2:uid="{FCE71247-BAFB-DC4D-8EC8-3FCE16968DC7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{FCE71247-BAFB-DC4D-8EC8-3FCE16968DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="123">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -57,13 +57,467 @@
   </si>
   <si>
     <t>Tình trạng (Pass/Fail)</t>
+  </si>
+  <si>
+    <t>TC1</t>
+  </si>
+  <si>
+    <t>Nhập đúng email, OTP và mật khẩu</t>
+  </si>
+  <si>
+    <t>TC2</t>
+  </si>
+  <si>
+    <t>TC3</t>
+  </si>
+  <si>
+    <t>TC4</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	nhập giá trị hợp lệ cho tất cả các trường
+-	nhập tên đăng nhập và mật khẩu không tồn tại trong bảng User
+2. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công -&gt; chuyển về trang chủ</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	nhập Email &gt;90 kí tự
+2. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email=nguyenhuudat337@gmail.com;OTP=123456; mật khẩu=Huudat1234@; </t>
+  </si>
+  <si>
+    <t>Email = huuda…....t@gmail.com</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi kí tự</t>
+  </si>
+  <si>
+    <t>Thông báo "Vui lòng nhập tối đa 90 ký tự"</t>
+  </si>
+  <si>
+    <t>Nhập email &gt;90 kí tự</t>
+  </si>
+  <si>
+    <t>Nhập email chứa dấu cách</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	nhập Email chứa dấu cách
+2. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = h uu @gmail.com</t>
+  </si>
+  <si>
+    <t>Thông báo "Phần đứng trước '@' không chứa biểu tượng ' ' "</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Để trống
+2. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = </t>
+  </si>
+  <si>
+    <t>Thông báo yêu cầu nhập</t>
+  </si>
+  <si>
+    <t>Thông báo "Nhập địa chỉ email"</t>
+  </si>
+  <si>
+    <t>TC5</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Email đã tồn tại 
+2. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = test@gmail.com</t>
+  </si>
+  <si>
+    <t>Thông báo "Email đã tồn tại"</t>
+  </si>
+  <si>
+    <t>Thông báo Email đã tồn tại</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Email sai định dạng
+2. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = testgmail.com</t>
+  </si>
+  <si>
+    <t>Thông báo Email  không đúng định dạng</t>
+  </si>
+  <si>
+    <t>Thông báo "vui lòng bao gồm '@'  trong địa chỉ email"</t>
+  </si>
+  <si>
+    <t>TC7</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP ít hơn 6 kí tự
+4. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = nguyenhuudat337@gmail.com ; OTP = 123</t>
+  </si>
+  <si>
+    <t>TC8</t>
+  </si>
+  <si>
+    <t>TC9</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP nhiều hơn 6 kí tự
+4. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = nguyenhuudat337@gmail.com ; OTP = 1234567</t>
+  </si>
+  <si>
+    <t>Nhập OTP là chữ</t>
+  </si>
+  <si>
+    <t>Nhập OTP nhiều hơn 6 kí tự</t>
+  </si>
+  <si>
+    <t>Nhập OTP ít hơn 6 kí tự</t>
+  </si>
+  <si>
+    <t>Nhập Email sai định dạng</t>
+  </si>
+  <si>
+    <t>Nhập Email đã tồn tại</t>
+  </si>
+  <si>
+    <t>Nhập Email để trống</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP là chữ
+4. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = nguyenhuudat337@gmail.com ; OTP = abcdef</t>
+  </si>
+  <si>
+    <t>Nhập OTP là kí tự đặc biệt</t>
+  </si>
+  <si>
+    <t>1.	Input data:
+-	Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP là kí tự đặc biệt
+4. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = nguyenhuudat337@gmail.com ; OTP = @@@!!!</t>
+  </si>
+  <si>
+    <t>Để trống OTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = </t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu ít hơn 8 kí tự</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Để trống OTP
+4. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu ít hơn 8 kí tự
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = Dat0911@</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi ít hơn 8 kí tự</t>
+  </si>
+  <si>
+    <t>Thông báo "Mật khẩu chưa hợp lệ. Đảm bảo đáp ứng các yêu cầu cho mật khẩu."</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu nhiều hơn 48 kí tự</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu nhiều hơn 8 kí tự
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = Datdattdattdattdattdattdat….....0911@</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi nhiều hơn 8 kí tự</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>Để trống mật khẩu</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Để trống mật khẩu
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu =   </t>
+  </si>
+  <si>
+    <t>Thông báo lỗi để trống</t>
+  </si>
+  <si>
+    <t>Thông báo "Vui lòng nhập trường này."</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu không có kí tự chữ hoa</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu không có kí tự chữ hoa
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = huudat0911@   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông báo lỗi thiếu kí tự </t>
+  </si>
+  <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu không có kí tự chữ thường</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu không có kí tự chữ thường
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = HUUDAT0911@   </t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu không có kí tự số</t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu không có kí tự số
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = Huudat@   </t>
+  </si>
+  <si>
+    <t>TC18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhập mật khẩu có dấu cách </t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu có dấu cách
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi không chứa dấu cách</t>
+  </si>
+  <si>
+    <t>TC19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhập mật khẩu không có kí tự đặc biệt </t>
+  </si>
+  <si>
+    <t>1. Input data:
+- Nhập email hợp lệ
+2. Click nút [xác nhận] 
+3. Input data:
+- Nhập OTP hợp lệ
+4. Click nút [xác nhận]
+5. Input data:
+- Nhập mật khẩu không có kí tự đặc biệt 
+6. Click nút [xác nhận]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = Huudat0911   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email = nguyenhuudat337@gmail.com ; OTP = 123456 ; Mật khẩu = Huu dat0911@   </t>
+  </si>
+  <si>
+    <t>Nhập hợp lệ tên loại sản phẩm</t>
+  </si>
+  <si>
+    <t>Input data:
+-	nhập giá trị hợp lệ cho  trường tìm kiếm loại sản phẩm</t>
+  </si>
+  <si>
+    <t>loại sản phẩm = áo khoác</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách các loại sản phẩm</t>
+  </si>
+  <si>
+    <t>Nhập tên loại sản phẩm chứa kí tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Input data:
+-	Nhập tên loại sản phẩm chứa kí tự đặc biệt</t>
+  </si>
+  <si>
+    <t>loại sản phẩm = @@@@</t>
+  </si>
+  <si>
+    <t>Không tìm thấy loại sản phẩm</t>
+  </si>
+  <si>
+    <t>Tìm thấy loại sản phẩm</t>
+  </si>
+  <si>
+    <t>Thông báo "Không có kết quả tìm kiếm cho '@'. Vui lòng thử lại"</t>
+  </si>
+  <si>
+    <t>Nhập tên loại sản phẩm chứa kí tự số</t>
+  </si>
+  <si>
+    <t>Input data:
+-	Nhập tên loại sản phẩm chứa kí tự số</t>
+  </si>
+  <si>
+    <t>loại sản phẩm = 1234</t>
+  </si>
+  <si>
+    <t>Thông báo "Không có kết quả tìm kiếm cho '123'. Vui lòng thử lại"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Để trống </t>
+  </si>
+  <si>
+    <t>Input data:
+-	Để trống tên loại sản phẩm</t>
+  </si>
+  <si>
+    <t>loại sản phẩm =</t>
+  </si>
+  <si>
+    <t>hệ thống tự gợi ý</t>
+  </si>
+  <si>
+    <t>Hệ thống gợi ý sản phẩm liên quan</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi không được để trống</t>
+  </si>
+  <si>
+    <t>Không thể kích nút "tiếp tục"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -84,6 +538,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -93,7 +553,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -116,15 +576,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,325 +959,663 @@
   <dimension ref="D5:J37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="1" max="3" width="10.83203125" style="2"/>
+    <col min="4" max="4" width="11.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="5" spans="4:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="2" t="s">
+    <row r="5" spans="4:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+    <row r="6" spans="4:10" ht="161" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="4:10" ht="142" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="4:10" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="4:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="4:10" ht="86" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="4:10" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="4:10" ht="139" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="4:10" ht="114" x14ac:dyDescent="0.2">
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="4:10" ht="114" x14ac:dyDescent="0.2">
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="4:10" ht="114" x14ac:dyDescent="0.2">
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="4:10" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="4:10" ht="234" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10" ht="197" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10" ht="209" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10" ht="221" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="4:10" ht="224" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="4:10" ht="214" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="4:10" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="4:10" ht="220" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="4:10" ht="38" x14ac:dyDescent="0.2">
+      <c r="D27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="4:10" ht="210" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="4:10" ht="142" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="4:10" ht="130" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="4:10" ht="229" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
     </row>
     <row r="34" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
     </row>
     <row r="36" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" spans="4:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testcasecuadat.xlsx
+++ b/testcasecuadat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huudat/KTPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8DAA0C-8B1A-6D47-AE5B-6495C3928675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E49D06-78C5-8442-ABB2-446516764F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{FCE71247-BAFB-DC4D-8EC8-3FCE16968DC7}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17080" xr2:uid="{FCE71247-BAFB-DC4D-8EC8-3FCE16968DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -619,7 +619,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
